--- a/docs/FCC-core-55-70/build46-item-walk-v1-2026-07-28.xlsx
+++ b/docs/FCC-core-55-70/build46-item-walk-v1-2026-07-28.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,6 +49,11 @@
     <font>
       <b val="1"/>
       <color rgb="00B45309"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0044546A"/>
       <sz val="10.5"/>
     </font>
   </fonts>
@@ -96,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -119,6 +124,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -562,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -574,6 +585,7 @@
     <col width="26" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -622,6 +634,11 @@
           <t>Your comments</t>
         </is>
       </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>Outcome (my status — kept current)</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
@@ -664,8 +681,17 @@
           <t>No mock needed — numbers, not layout</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr"/>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 46 — given verbally, 2026-07-29 ("build all 16")</t>
+        </is>
+      </c>
       <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>BUILT — odds read the claim-age-adjusted check everywhere (hub = SS screen, agreement-pinned; the legacy cockpit fixed too)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="95" customHeight="1">
       <c r="A4" s="5" t="n">
@@ -701,8 +727,17 @@
           <t>Matches the detail page’s approved treatment; say "show me" for a drawn row first</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 46 — given verbally, 2026-07-29 ("build all 16")</t>
+        </is>
+      </c>
       <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>BUILT — unpriced rows show what you paid, in words; no weight % (0% would be wrong)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="95" customHeight="1">
       <c r="A5" s="5" t="n">
@@ -738,8 +773,17 @@
           <t>No mock needed</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr"/>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 46 — given verbally, 2026-07-29 ("build all 16")</t>
+        </is>
+      </c>
       <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>BUILT — the pop-up masks its title and body like every surface</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -782,8 +826,17 @@
           <t>Activity list already in your approved account-detail FINAL mock</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 46 — given verbally, 2026-07-29 ("build all 16")</t>
+        </is>
+      </c>
       <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>BUILT — bond/alternative partial sales write a SELL activity row; the ledger (not a silent patch) lowers the value</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="95" customHeight="1">
       <c r="A8" s="5" t="n">
@@ -819,8 +872,17 @@
           <t>No mock needed</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 46 — given verbally, 2026-07-29 ("build all 16")</t>
+        </is>
+      </c>
       <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>BUILT — one shared market-average formula behind Home and Invest, source-pinned</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="95" customHeight="1">
       <c r="A9" s="5" t="n">
@@ -856,8 +918,17 @@
           <t>No mock needed</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 46 — given verbally, 2026-07-29 ("build all 16")</t>
+        </is>
+      </c>
       <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>BUILT — equity lands in its vest months on the income year view too; one shared placement rule, agreement-pinned</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -900,8 +971,17 @@
           <t>Drawn in networth-v7 FINAL (open it — you are looking at it)</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 46 — given verbally, 2026-07-29 ("build all 16")</t>
+        </is>
+      </c>
       <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>BUILT — the path-ahead row renders per your v7 mock; the projection number appears only when the plan is computable</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="95" customHeight="1">
       <c r="A12" s="5" t="n">
@@ -937,8 +1017,17 @@
           <t>Drawn in networth-v7 FINAL</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 46 — given verbally, 2026-07-29 ("build all 16")</t>
+        </is>
+      </c>
       <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>BUILT — By class / By institution / By type pills; institution and type views roll whole accounts under one header</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="95" customHeight="1">
       <c r="A13" s="5" t="n">
@@ -974,8 +1063,17 @@
           <t>Drawn in home-v2 (approved)</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 46 — given verbally, 2026-07-29 ("build all 16")</t>
+        </is>
+      </c>
       <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>BUILT — dollar-first wording on cash-drag and account-concentration; the instruction became a fact</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -1018,8 +1116,17 @@
           <t>Words only</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 46 — given verbally, 2026-07-29 ("build all 16")</t>
+        </is>
+      </c>
       <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>BUILT — yearly interest (APR), Yield to maturity, Required withdrawals (RMD)</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="95" customHeight="1">
       <c r="A16" s="5" t="n">
@@ -1055,8 +1162,17 @@
           <t>Your copy IS the approval</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 46 — given verbally, 2026-07-29 ("build all 16")</t>
+        </is>
+      </c>
       <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>NO CODE CHANGE NEEDED — git shows the shipped text IS your approved 2026-07-19 copy; the DESIGN DOC was stale and now carries it. Paste your original if you remember it differently.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="95" customHeight="1">
       <c r="A17" s="5" t="n">
@@ -1092,8 +1208,17 @@
           <t>Approved sentences exist</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 46 — given verbally, 2026-07-29 ("build all 16")</t>
+        </is>
+      </c>
       <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="10" t="inlineStr">
+        <is>
+          <t>BUILT — one shared estimate tag component + one trying-it-out sentence on all three scenario surfaces + the approved Debts first-open line</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="95" customHeight="1">
       <c r="A18" s="5" t="n">
@@ -1129,8 +1254,17 @@
           <t>Spacing only</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 46 — given verbally, 2026-07-29 ("build all 16")</t>
+        </is>
+      </c>
       <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>BUILT — flagged rows and links raised to 44pt; a ratchet test keeps any sub-44 from returning on those surfaces</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="95" customHeight="1">
       <c r="A19" s="5" t="n">
@@ -1166,8 +1300,17 @@
           <t>Doc-specified words</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 46 — given verbally, 2026-07-29 ("build all 16")</t>
+        </is>
+      </c>
       <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="10" t="inlineStr">
+        <is>
+          <t>BUILT — "This year ~$…" and "See July’s paycheck →" (names the current month)</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="95" customHeight="1">
       <c r="A20" s="5" t="n">
@@ -1203,8 +1346,17 @@
           <t>No mock needed</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 46 — given verbally, 2026-07-29 ("build all 16")</t>
+        </is>
+      </c>
       <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="10" t="inlineStr">
+        <is>
+          <t>BUILT as a CLASS — spoken labels across 16 files now say "hidden"; a guard test blocks the dot characters from ever re-entering a spoken label</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
@@ -1247,8 +1399,17 @@
           <t>Words only; behavior already matches</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>APPROVE FOR BUILD 46 — given verbally, 2026-07-29 ("build all 16")</t>
+        </is>
+      </c>
       <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>BUILT — one promise in consent and Settings: you choose, keep as by-hand or delete</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
